--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Reserva Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Reserva Muestreo Datos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CFFC7C-C5C9-4E03-82A0-BB5540DADFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB6E770-51C8-4A20-AC64-0F9502193E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{37DFAE61-0D86-49EA-8370-168CB72B907A}"/>
   </bookViews>
@@ -667,8 +667,8 @@
       <sheetName val="Inmueble"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="4">
           <cell r="E4" t="str">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="E4" s="8" t="str">
         <f ca="1">TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>14</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E5" s="8" t="str">
         <f t="shared" ref="E5:E10" ca="1" si="0">TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>16</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>14</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E7" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>14</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E8" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>14</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E9" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>16</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="E10" s="8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>13/10/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>14</v>

--- a/Doo-Doc/Nueva Version Victus/MuestreoDatos/Reserva Muestreo Datos.xlsx
+++ b/Doo-Doc/Nueva Version Victus/MuestreoDatos/Reserva Muestreo Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\MuestreoDatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB6E770-51C8-4A20-AC64-0F9502193E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29936AB-5FEF-405A-9C7C-692E7CDEEC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{37DFAE61-0D86-49EA-8370-168CB72B907A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{37DFAE61-0D86-49EA-8370-168CB72B907A}"/>
   </bookViews>
   <sheets>
     <sheet name="Objetos de dominio" sheetId="1" r:id="rId1"/>
@@ -559,7 +559,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -570,12 +570,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -602,21 +596,9 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
@@ -636,6 +618,39 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -667,57 +682,57 @@
       <sheetName val="Inmueble"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="4">
           <cell r="E4" t="str">
-            <v>Apartamento102 - Torre1 - Forest apartamentos</v>
+            <v>Apartamento</v>
           </cell>
         </row>
         <row r="5">
           <cell r="E5" t="str">
-            <v>Casa10 - Bloque1 - Forest apartamentos</v>
+            <v>Apartamento</v>
           </cell>
         </row>
         <row r="6">
           <cell r="E6" t="str">
-            <v>Apartamento304 - Torre2 - Forest apartamentos</v>
+            <v>Casa</v>
           </cell>
         </row>
         <row r="7">
           <cell r="E7" t="str">
-            <v>Casa11 - Bloque1 - Natural</v>
+            <v>Casa</v>
           </cell>
         </row>
         <row r="8">
           <cell r="E8" t="str">
-            <v>Apartamento423 - Bloque1 - Ventus</v>
+            <v>Apartamento</v>
           </cell>
         </row>
         <row r="9">
           <cell r="E9" t="str">
-            <v>Apartamento1204 - Torre1 - Bolivar</v>
+            <v>Casa</v>
           </cell>
         </row>
         <row r="10">
           <cell r="E10" t="str">
-            <v>Casa5 - Bloque1 - Natural</v>
+            <v>Apartamento</v>
           </cell>
         </row>
         <row r="11">
           <cell r="E11" t="str">
-            <v>Casa17 - Bloque2 - Riogrande</v>
+            <v>Casa</v>
           </cell>
         </row>
         <row r="12">
           <cell r="E12" t="str">
-            <v>Apartamento514 - Bloque1 - Riogrande</v>
+            <v>Apartamento</v>
           </cell>
         </row>
         <row r="13">
           <cell r="E13" t="str">
-            <v>Casa23 - Bloque1 - Natural</v>
+            <v>Casa</v>
           </cell>
         </row>
       </sheetData>
@@ -1044,13 +1059,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C361087-9E97-4542-829D-B3B83CB492EF}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1066,7 +1081,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1094,261 +1109,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5276C67-4ACF-4F34-ACBA-8F9695F1FA3D}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="130.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="23.5546875" customWidth="1"/>
-    <col min="7" max="7" width="223" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="89.42578125" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
+    <col min="5" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="79.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:7" s="30" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:7" s="27" customFormat="1" ht="81" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="27" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="43" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="28">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="44">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="31" t="str">
+      <c r="C4" s="45" t="str">
         <f>Turno!$G$6</f>
         <v xml:space="preserve">Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="46" t="str">
         <f>Residente!$K$4</f>
         <v>Cédula de Ciudadanía-74564891</v>
       </c>
-      <c r="E4" s="8" t="str">
+      <c r="E4" s="47" t="str">
         <f ca="1">TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F4" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F4" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="10" t="str">
+      <c r="G4" s="49" t="str">
         <f>C4&amp;"-"&amp;D4</f>
         <v>Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. -Cédula de Ciudadanía-74564891</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="44">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31" t="str">
+      <c r="C5" s="45" t="str">
         <f>Turno!$G$9</f>
         <v xml:space="preserve">Turno 2-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 5:00:00 p. m. - 7:00:00 p. m. </v>
       </c>
-      <c r="D5" s="33" t="str">
+      <c r="D5" s="46" t="str">
         <f>Residente!$K$5</f>
         <v>Registro civil-16513516</v>
       </c>
-      <c r="E5" s="8" t="str">
+      <c r="E5" s="47" t="str">
         <f t="shared" ref="E5:E10" ca="1" si="0">TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F5" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F5" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G5" s="49" t="str">
         <f t="shared" ref="G5:G10" si="1">C5&amp;"-"&amp;D5</f>
         <v>Turno 2-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 5:00:00 p. m. - 7:00:00 p. m. -Registro civil-16513516</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="44">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="31" t="str">
+      <c r="C6" s="45" t="str">
         <f>Turno!$G$13</f>
         <v xml:space="preserve">Turno 3-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 12:00:00 p. m. - 1:00:00 p. m. </v>
       </c>
-      <c r="D6" s="33" t="str">
+      <c r="D6" s="46" t="str">
         <f>Residente!$K$6</f>
         <v>Pasaporte-8552369</v>
       </c>
-      <c r="E6" s="8" t="str">
+      <c r="E6" s="47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F6" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F6" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="10" t="str">
+      <c r="G6" s="49" t="str">
         <f t="shared" si="1"/>
         <v>Turno 3-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 12:00:00 p. m. - 1:00:00 p. m. -Pasaporte-8552369</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="32" t="str">
+      <c r="C7" s="50" t="str">
         <f>Turno!$G$10</f>
         <v xml:space="preserve">Turno 3-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 7:00:00 p. m. - 9:00:00 p. m. </v>
       </c>
-      <c r="D7" s="33" t="str">
+      <c r="D7" s="46" t="str">
         <f>Residente!K9</f>
         <v>Cédula de Ciudadanía-1034567890</v>
       </c>
-      <c r="E7" s="8" t="str">
+      <c r="E7" s="47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F7" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F7" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="10" t="str">
+      <c r="G7" s="49" t="str">
         <f t="shared" si="1"/>
         <v>Turno 3-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 7:00:00 p. m. - 9:00:00 p. m. -Cédula de Ciudadanía-1034567890</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="44">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="32" t="str">
+      <c r="C8" s="50" t="str">
         <f>Turno!G12</f>
         <v xml:space="preserve">Turno 2-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
-      <c r="D8" s="33" t="str">
+      <c r="D8" s="46" t="str">
         <f>Residente!K10</f>
         <v>Tarjeta de Identidad-900123456</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F8" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="10" t="str">
+      <c r="G8" s="49" t="str">
         <f t="shared" si="1"/>
         <v>Turno 2-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. -Tarjeta de Identidad-900123456</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="32" t="str">
+      <c r="C9" s="50" t="str">
         <f>Turno!G6</f>
         <v xml:space="preserve">Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
-      <c r="D9" s="33" t="str">
+      <c r="D9" s="46" t="str">
         <f>Residente!K11</f>
         <v>Pasaporte-1045678901</v>
       </c>
-      <c r="E9" s="8" t="str">
+      <c r="E9" s="47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F9" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F9" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="10" t="str">
+      <c r="G9" s="49" t="str">
         <f t="shared" si="1"/>
         <v>Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. -Pasaporte-1045678901</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="44">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="32" t="str">
+      <c r="C10" s="50" t="str">
         <f>Turno!$G$8</f>
         <v xml:space="preserve">Turno 1-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 3:00:00 p. m. - 5:00:00 p. m. </v>
       </c>
-      <c r="D10" s="33" t="str">
+      <c r="D10" s="46" t="str">
         <f>Residente!K13</f>
         <v>Cédula de Ciudadanía-1067890123</v>
       </c>
-      <c r="E10" s="8" t="str">
+      <c r="E10" s="47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/10/2024</v>
-      </c>
-      <c r="F10" s="9" t="s">
+        <v>02/11/2024</v>
+      </c>
+      <c r="F10" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="10" t="str">
+      <c r="G10" s="49" t="str">
         <f t="shared" si="1"/>
         <v>Turno 1-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 3:00:00 p. m. - 5:00:00 p. m. -Cédula de Ciudadanía-1067890123</v>
       </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1378,50 +1429,50 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB08A702-FD28-42AA-96CF-A0FF0C0CE614}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="133.6640625" customWidth="1"/>
-    <col min="7" max="7" width="140.6640625" customWidth="1"/>
+    <col min="3" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="133.7109375" customWidth="1"/>
+    <col min="7" max="7" width="140.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
       <c r="F1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="27" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1444,440 +1495,440 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>0.25</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G4" s="10" t="str">
+      <c r="G4" s="8" t="str">
         <f>_xlfn.CONCAT(B4,"-",F4,"-",TEXT(C4," h:mm:ss AM/PM "),"-",TEXT(D4," h:mm:ss AM/PM "))</f>
         <v xml:space="preserve">Turno 1-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 6:00:00 a. m. - 8:00:00 a. m. </v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G5" s="8" t="str">
         <f t="shared" ref="G5:G21" si="0">_xlfn.CONCAT(B5,"-",F5,"-",TEXT(C5," h:mm:ss AM/PM "),"-",TEXT(D5," h:mm:ss AM/PM "))</f>
         <v xml:space="preserve">Turno 2-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 8:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>0.5</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="10" t="str">
+      <c r="G6" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 10:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="10">
         <v>0.54166666666666696</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="10">
         <v>0.58333333333333404</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="10" t="str">
+      <c r="G7" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Piscina-Forest apartamentos - 18  septiembre 2024 6:00:00 a. m.  hasta - 18  septiembre 2024 2:00:00 p. m. - 1:00:00 p. m. - 2:00:00 p. m. </v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>0.625</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="10" t="str">
+      <c r="G8" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 3:00:00 p. m. - 5:00:00 p. m. </v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>0.70833333333333337</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <v>0.79166666666666663</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="10" t="str">
+      <c r="G9" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 5:00:00 p. m. - 7:00:00 p. m. </v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <v>0.875</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="10" t="str">
+      <c r="G10" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Gimnasio-Forest apartamentos - 18  septiembre 2024 3:00:00 p. m.  hasta - 18  septiembre 2024 9:00:00 p. m. - 7:00:00 p. m. - 9:00:00 p. m. </v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="16">
         <v>0.95833333333333337</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="10" t="str">
+      <c r="G11" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 10:00:00 p. m. - 11:00:00 p. m. </v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="16">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="16">
         <v>0.5</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="10" t="str">
+      <c r="G12" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>10</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>0.5</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="16">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="10" t="str">
+      <c r="G13" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-piscinaAdultos-Natural - 20  septiembre 2024 10:00:00 a. m.  hasta - 20  septiembre 2024 1:00:00 p. m. - 12:00:00 p. m. - 1:00:00 p. m. </v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="20">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
         <v>11</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="19">
         <v>0.375</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="10" t="str">
+      <c r="G14" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="20">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
         <v>12</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="19">
         <v>0.375</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="19">
         <v>0.41666666666666702</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="10" t="str">
+      <c r="G15" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="20">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
         <v>13</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="19">
         <v>0.41666666666666702</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="19">
         <v>0.45833333333333398</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="10" t="str">
+      <c r="G16" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="20">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
         <v>14</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>0.45833333333333398</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="19">
         <v>0.500000000000001</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="10" t="str">
+      <c r="G17" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Salón de Eventos-Riogrande - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="38">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="32">
         <v>15</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="33">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="33">
         <v>0.375</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G18" s="10" t="str">
+      <c r="G18" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 1-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 8:00:00 a. m. - 9:00:00 a. m. </v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="38">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="32">
         <v>16</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="33">
         <v>0.375</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="33">
         <v>0.41666666666666702</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="10" t="str">
+      <c r="G19" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 2-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 9:00:00 a. m. - 10:00:00 a. m. </v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="38">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="32">
         <v>17</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="33">
         <v>0.41666666666666702</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="33">
         <v>0.45833333333333398</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="10" t="str">
+      <c r="G20" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 3-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 10:00:00 a. m. - 11:00:00 a. m. </v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="38">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="32">
         <v>18</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="33">
         <v>0.45833333333333398</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="33">
         <v>0.500000000000001</v>
       </c>
-      <c r="E21" s="40" t="s">
+      <c r="E21" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="G21" s="10" t="str">
+      <c r="G21" s="8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">Turno 4-Cancha de Fútbol-Bolivar - 18  septiembre 2024 8:00:00 a. m.  hasta - 18  septiembre 2024 12:00:00 p. m. - 11:00:00 a. m. - 12:00:00 p. m. </v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="20">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
         <v>19</v>
       </c>
       <c r="B22" s="4"/>
@@ -1885,13 +1936,13 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="41" t="str">
+      <c r="G22" s="35" t="str">
         <f t="shared" ref="G22:G27" si="1">_xlfn.CONCAT(B22,"-",F22)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="20">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="4"/>
@@ -1899,13 +1950,13 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="41" t="str">
+      <c r="G23" s="35" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="20">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
         <v>21</v>
       </c>
       <c r="B24" s="4"/>
@@ -1913,13 +1964,13 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="41" t="str">
+      <c r="G24" s="35" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="20">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="4"/>
@@ -1927,13 +1978,13 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="41" t="str">
+      <c r="G25" s="35" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="20">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
         <v>23</v>
       </c>
       <c r="B26" s="4"/>
@@ -1941,13 +1992,13 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="41" t="str">
+      <c r="G26" s="35" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="20">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="4"/>
@@ -1955,13 +2006,13 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="41" t="str">
+      <c r="G27" s="35" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="20">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
         <v>25</v>
       </c>
       <c r="B28" s="4"/>
@@ -1970,13 +2021,13 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F29" s="42"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F30" s="42"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F30" s="36"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F31" t="s">
         <v>107</v>
       </c>
@@ -2012,27 +2063,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F107DE-6D7F-46D5-A5A6-9AD6DF906ACB}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="6" width="21.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.88671875" customWidth="1"/>
-    <col min="8" max="8" width="23.5546875" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" customWidth="1"/>
-    <col min="10" max="10" width="50.5546875" customWidth="1"/>
+    <col min="3" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="50.5703125" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" customWidth="1"/>
     <col min="13" max="13" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
@@ -2040,48 +2091,48 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:13" s="44" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+    <row r="2" spans="1:13" s="38" customFormat="1" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="K2" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="L2" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="43" t="s">
+      <c r="M2" s="37" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2122,142 +2173,142 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <v>74564891</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="23">
         <v>36689</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>3053456459</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="45" t="str">
+      <c r="J4" s="39" t="str">
         <f>[1]Inmueble!E4</f>
-        <v>Apartamento102 - Torre1 - Forest apartamentos</v>
-      </c>
-      <c r="K4" s="27" t="str">
+        <v>Apartamento</v>
+      </c>
+      <c r="K4" s="25" t="str">
         <f>_xlfn.CONCAT(D4,"-",E4)</f>
         <v>Cédula de Ciudadanía-74564891</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="25">
         <f>G4</f>
         <v>3053456459</v>
       </c>
-      <c r="M4" s="27" t="str">
+      <c r="M4" s="25" t="str">
         <f>H4</f>
         <v>example@example.com</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="21" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <v>16513516</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="23">
         <v>38315</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>3015124578</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="45" t="str">
+      <c r="J5" s="39" t="str">
         <f>[1]Inmueble!E5</f>
-        <v>Casa10 - Bloque1 - Forest apartamentos</v>
-      </c>
-      <c r="K5" s="27" t="str">
+        <v>Apartamento</v>
+      </c>
+      <c r="K5" s="25" t="str">
         <f t="shared" ref="K5:K13" si="0">_xlfn.CONCAT(D5,"-",E5)</f>
         <v>Registro civil-16513516</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="25">
         <f t="shared" ref="L5:M13" si="1">G5</f>
         <v>3015124578</v>
       </c>
-      <c r="M5" s="27" t="str">
+      <c r="M5" s="25" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">ejemplo@jueves.com </v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <v>8552369</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="23">
         <v>35494</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <v>3057477830</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="26" t="str">
+      <c r="J6" s="24" t="str">
         <f>[1]Inmueble!E6</f>
-        <v>Apartamento304 - Torre2 - Forest apartamentos</v>
-      </c>
-      <c r="K6" s="27" t="str">
+        <v>Casa</v>
+      </c>
+      <c r="K6" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Pasaporte-8552369</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="25">
         <f t="shared" si="1"/>
         <v>3057477830</v>
       </c>
-      <c r="M6" s="27" t="str">
+      <c r="M6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>andresjobpk@gmail.com</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -2273,36 +2324,36 @@
       <c r="E7" s="4">
         <v>1012345678</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="26">
         <v>32944</v>
       </c>
       <c r="G7" s="4">
         <v>3102345678</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="24" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="26" t="str">
+      <c r="J7" s="24" t="str">
         <f>[1]Inmueble!E7</f>
-        <v>Casa11 - Bloque1 - Natural</v>
-      </c>
-      <c r="K7" s="27" t="str">
+        <v>Casa</v>
+      </c>
+      <c r="K7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Cédula de Ciudadanía-1012345678</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="25">
         <f t="shared" si="1"/>
         <v>3102345678</v>
       </c>
-      <c r="M7" s="27" t="str">
+      <c r="M7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>alejandro.perez90@mail.com</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -2318,36 +2369,36 @@
       <c r="E8" s="4">
         <v>1023456789</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="26">
         <v>31253</v>
       </c>
       <c r="G8" s="4">
         <v>3204567890</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="24" t="s">
         <v>65</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="26" t="str">
+      <c r="J8" s="24" t="str">
         <f>[1]Inmueble!E8</f>
-        <v>Apartamento423 - Bloque1 - Ventus</v>
-      </c>
-      <c r="K8" s="27" t="str">
+        <v>Apartamento</v>
+      </c>
+      <c r="K8" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Cédula de extranjería-1023456789</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="25">
         <f t="shared" si="1"/>
         <v>3204567890</v>
       </c>
-      <c r="M8" s="27" t="str">
+      <c r="M8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>maria.gomez85@mail.com</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>6</v>
       </c>
@@ -2363,36 +2414,36 @@
       <c r="E9" s="4">
         <v>1034567890</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="26">
         <v>35013</v>
       </c>
       <c r="G9" s="4">
         <v>3156781234</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="24" t="s">
         <v>68</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="26" t="str">
+      <c r="J9" s="24" t="str">
         <f>[1]Inmueble!E9</f>
-        <v>Apartamento1204 - Torre1 - Bolivar</v>
-      </c>
-      <c r="K9" s="27" t="str">
+        <v>Casa</v>
+      </c>
+      <c r="K9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Cédula de Ciudadanía-1034567890</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="25">
         <f t="shared" si="1"/>
         <v>3156781234</v>
       </c>
-      <c r="M9" s="27" t="str">
+      <c r="M9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>juan.rodriguez95@mail.com</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -2408,36 +2459,36 @@
       <c r="E10" s="4">
         <v>900123456</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="26">
         <v>36560</v>
       </c>
       <c r="G10" s="4">
         <v>3112345678</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="24" t="s">
         <v>72</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="26" t="str">
+      <c r="J10" s="24" t="str">
         <f>[1]Inmueble!E10</f>
-        <v>Casa5 - Bloque1 - Natural</v>
-      </c>
-      <c r="K10" s="27" t="str">
+        <v>Apartamento</v>
+      </c>
+      <c r="K10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Tarjeta de Identidad-900123456</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="25">
         <f t="shared" si="1"/>
         <v>3112345678</v>
       </c>
-      <c r="M10" s="27" t="str">
+      <c r="M10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>camila.torres00@mail.com</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -2453,13 +2504,13 @@
       <c r="E11" s="4">
         <v>1045678901</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="26">
         <v>33867</v>
       </c>
       <c r="G11" s="4">
         <v>3149876543</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="24" t="s">
         <v>76</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2467,22 +2518,22 @@
       </c>
       <c r="J11" s="2" t="str">
         <f>[1]Inmueble!E11</f>
-        <v>Casa17 - Bloque2 - Riogrande</v>
-      </c>
-      <c r="K11" s="27" t="str">
+        <v>Casa</v>
+      </c>
+      <c r="K11" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Pasaporte-1045678901</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="25">
         <f t="shared" si="1"/>
         <v>3149876543</v>
       </c>
-      <c r="M11" s="27" t="str">
+      <c r="M11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>andres.garcia92@mail.com</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -2498,13 +2549,13 @@
       <c r="E12" s="4">
         <v>1056789012</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="26">
         <v>34128</v>
       </c>
       <c r="G12" s="4">
         <v>3135678901</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="24" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="4" t="s">
@@ -2512,22 +2563,22 @@
       </c>
       <c r="J12" s="2" t="str">
         <f>[1]Inmueble!E12</f>
-        <v>Apartamento514 - Bloque1 - Riogrande</v>
-      </c>
-      <c r="K12" s="27" t="str">
+        <v>Apartamento</v>
+      </c>
+      <c r="K12" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Cédula de Ciudadanía-1056789012</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="25">
         <f t="shared" si="1"/>
         <v>3135678901</v>
       </c>
-      <c r="M12" s="27" t="str">
+      <c r="M12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>laura.martinez93@mail.com</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -2543,13 +2594,13 @@
       <c r="E13" s="4">
         <v>1067890123</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="26">
         <v>32507</v>
       </c>
       <c r="G13" s="4">
         <v>3123456789</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>84</v>
       </c>
       <c r="I13" s="4" t="s">
@@ -2557,17 +2608,17 @@
       </c>
       <c r="J13" s="2" t="str">
         <f>[1]Inmueble!E13</f>
-        <v>Casa23 - Bloque1 - Natural</v>
-      </c>
-      <c r="K13" s="27" t="str">
+        <v>Casa</v>
+      </c>
+      <c r="K13" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Cédula de Ciudadanía-1067890123</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="25">
         <f t="shared" si="1"/>
         <v>3123456789</v>
       </c>
-      <c r="M13" s="27" t="str">
+      <c r="M13" s="25" t="str">
         <f t="shared" si="1"/>
         <v>felipe.ramirez88@mail.com</v>
       </c>
